--- a/D6_results/01_Quincy_D6_Workbook_FINAL_SUBMISSION.xlsx
+++ b/D6_results/01_Quincy_D6_Workbook_FINAL_SUBMISSION.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="Re5e65f37a4b1457e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="2" r:id="Rb67b3f7597c745ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Run Ledger" sheetId="3" r:id="R9277c3a146a44932"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model Summary" sheetId="4" r:id="Rbbab3b97ae54450f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity" sheetId="5" r:id="Re09b8bd89b92412b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Break Even" sheetId="6" r:id="R0e3ce3131d5a449c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="My Eval Cases" sheetId="7" r:id="Rd56378a5e3a94a9f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="V1 Pass Evidence" sheetId="8" r:id="R828091055df8402c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R24fb4f74233b4343"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="2" r:id="Ree5a10198bd74469"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Run Ledger" sheetId="3" r:id="R2ecd19a780cf4082"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model Summary" sheetId="4" r:id="R13c3bf6be5494b6d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity" sheetId="5" r:id="Rb5dd9c6221c54784"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Break Even" sheetId="6" r:id="R2780e6f4d5fc455b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="My Eval Cases" sheetId="7" r:id="R0036b68f12244dd7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="V1 Pass Evidence" sheetId="8" r:id="R3c0099db8e184132"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -6466,16 +6466,16 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="C7" s="72" t="n">
-        <x:v>0.6666666667</x:v>
+        <x:v>0.6833333333333333</x:v>
       </x:c>
       <x:c r="D7" s="72" t="n">
-        <x:v>0.6666666667</x:v>
+        <x:v>0.65</x:v>
       </x:c>
       <x:c r="E7" s="74" t="n">
-        <x:v>15141.4</x:v>
+        <x:v>13725.42</x:v>
       </x:c>
       <x:c r="F7" s="74" t="n">
-        <x:v>1683.52</x:v>
+        <x:v>1521.45</x:v>
       </x:c>
       <x:c r="G7" s="76" t="n">
         <x:v>0.0679</x:v>
@@ -6485,18 +6485,18 @@
       </x:c>
       <x:c r="I7" s="78" t="n">
         <x:f>(E7*G7+F7*H7)/1000000</x:f>
-        <x:v>0.0013109324200000002</x:v>
+        <x:v>0.0011875596180000003</x:v>
       </x:c>
       <x:c r="J7" s="78" t="n">
         <x:f>I7+(1-D7)*Assumptions!$B$7+Assumptions!$B$11</x:f>
-        <x:v>2.5346442655000003</x:v>
+        <x:v>2.661187559618</x:v>
       </x:c>
       <x:c r="K7" s="80" t="n">
         <x:f>J7*Assumptions!$B$8</x:f>
-        <x:v>20277.154124000004</x:v>
+        <x:v>21289.500476944</x:v>
       </x:c>
       <x:c r="L7" s="69" t="str">
-        <x:v>Summary + saved notebook output</x:v>
+        <x:v>D5b DeepSeek summary CSV</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="14.600000381469727">
